--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>49308.13</v>
+        <v>49054.78</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29061.41</v>
+        <v>29266.52</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>42607.59</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29679.76</v>
+        <v>29638.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>59362.12</v>
+        <v>59770.72</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>387809.16</v>
+        <v>382886.76</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46111.52</v>
+        <v>45526.23</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>54476.77</v>
+        <v>54610.8</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41289.58</v>
+        <v>40758.02</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>35594.33</v>
+        <v>35136.09</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>62277.37</v>
+        <v>62331.02</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30549.71</v>
+        <v>30107.74</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>79354.7</v>
+        <v>79604.38</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>70563.2</v>
+        <v>69795.59</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44633.81</v>
+        <v>44295.21</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>29496.28</v>
+        <v>29091</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>48407.97</v>
+        <v>47413.1</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>43518.97</v>
+        <v>43688.38</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,68 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30611.34</v>
+        <v>30816.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>527481-81-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>30303.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>627786-239-CM25</t>
+          <t>2997-57-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>49054.78</v>
+        <v>51145.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>727202-3302-CM25</t>
+          <t>1346282-119-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29266.52</v>
+        <v>28740.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3276-37-CM25</t>
+          <t>727202-3279-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>42066.38</v>
+        <v>35085.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>727202-3316-CM25</t>
+          <t>627786-239-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29638.13</v>
+        <v>49054.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2446-2409-CM25</t>
+          <t>727202-3302-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>59770.72</v>
+        <v>29266.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624-379-CM25</t>
+          <t>3276-37-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,24 +867,20 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Región del Ñuble</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>382886.76</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3754-1-CM26</t>
+          <t>727202-3316-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45526.23</v>
+        <v>29638.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3614-31-CM26</t>
+          <t>2446-2409-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>54610.8</v>
+        <v>59770.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2446-252-CM26</t>
+          <t>624-379-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,28 +1042,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Región del Ñuble</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>40758.02</v>
+        <v>382886.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1395-120-CM26</t>
+          <t>3754-1-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>35136.09</v>
+        <v>45526.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>527481-29-CM26</t>
+          <t>3614-31-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>62331.02</v>
+        <v>54610.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2448-230-CM26</t>
+          <t>2446-252-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,43 +1244,43 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30107.74</v>
+        <v>40758.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3753-144-CM26</t>
+          <t>1395-120-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>79604.38</v>
+        <v>35136.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>703036-12-CM26</t>
+          <t>527481-29-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,28 +1366,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>69795.59</v>
+        <v>62331.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3712-361-CM26</t>
+          <t>2448-230-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44295.21</v>
+        <v>30107.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2997-66-CM26</t>
+          <t>3753-144-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>29091</v>
+        <v>79604.38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1180825-16-CM26</t>
+          <t>703036-12-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>47413.1</v>
+        <v>69795.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>624-133-CM26</t>
+          <t>3712-361-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>43688.38</v>
+        <v>44295.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>646-74-CM26</t>
+          <t>2997-66-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30816.24</v>
+        <v>29091</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>527481-81-CM26</t>
+          <t>1180825-16-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,6 +1732,189 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
+        <v>47413.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>624-133-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>43688.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>646-74-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.816.000-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>30816.24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>527481-81-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>30303.8</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2997-57-CM25</t>
+          <t>1305532-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>51145.64</v>
+        <v>24005.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1346282-119-CM25</t>
+          <t>3707-90-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>28740.62</v>
+        <v>70343.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>727202-3279-CM25</t>
+          <t>3512-2792-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>35085.11</v>
+        <v>32720.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>627786-239-CM25</t>
+          <t>3614-38-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>49054.78</v>
+        <v>17823.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>727202-3302-CM25</t>
+          <t>3512-2813-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>29266.52</v>
+        <v>53204.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3276-37-CM25</t>
+          <t>2997-57-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>42066.38</v>
+        <v>51145.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>727202-3316-CM25</t>
+          <t>1346282-119-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>29638.13</v>
+        <v>28740.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2446-2409-CM25</t>
+          <t>646-33-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>59770.72</v>
+        <v>24828.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>624-379-CM25</t>
+          <t>3509-214-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,32 +1042,28 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Región del Ñuble</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>382886.76</v>
+        <v>36525.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3754-1-CM26</t>
+          <t>1094-3-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45526.23</v>
+        <v>26458.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3614-31-CM26</t>
+          <t>539119-3510-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>54610.8</v>
+        <v>31850.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2446-252-CM26</t>
+          <t>4784-16-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>40758.02</v>
+        <v>26312.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1395-120-CM26</t>
+          <t>3842-19-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35136.09</v>
+        <v>36157.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>527481-29-CM26</t>
+          <t>624-204-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>62331.02</v>
+        <v>24277.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2448-230-CM26</t>
+          <t>3712-769-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30107.74</v>
+        <v>26904.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3753-144-CM26</t>
+          <t>3712-685-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>79604.38</v>
+        <v>70601.14999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>703036-12-CM26</t>
+          <t>2448-745-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,33 +1545,33 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>69795.59</v>
+        <v>42202.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3712-361-CM26</t>
+          <t>3712-799-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>44295.21</v>
+        <v>36460.55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2997-66-CM26</t>
+          <t>624-318-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>29091</v>
+        <v>35782.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1180825-16-CM26</t>
+          <t>727202-3280-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>47413.1</v>
+        <v>35085.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>624-133-CM26</t>
+          <t>727202-3279-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,43 +1789,43 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>43688.38</v>
+        <v>35085.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>646-74-CM26</t>
+          <t>627786-239-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>30816.24</v>
+        <v>49054.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>527481-81-CM26</t>
+          <t>727202-3302-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,7 +1911,1292 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
+        <v>29266.52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3276-37-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>42066.38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>727202-3316-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.040.500-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>29638.13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2446-2409-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>59770.72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>624-379-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>382886.76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3754-1-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>45526.23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3614-31-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.040.500-8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>54610.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1395-120-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>35136.09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2446-252-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>40758.02</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>527481-29-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>62331.02</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2448-230-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>30107.74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3753-144-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>79604.38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>703036-12-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>69795.59</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3712-361-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>44295.21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2997-66-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.040.800-7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>29091</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1180825-16-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.606.400-2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>47413.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>624-133-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>43688.38</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>646-74-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.816.000-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>30816.24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3713-95-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>36317.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3713-96-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>762.03</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>527481-81-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
         <v>30303.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3754-198-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>36103.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2226,7 +2226,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3614-31-CM26</t>
+          <t>1107276-37-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>54610.8</v>
+        <v>26204.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1395-120-CM26</t>
+          <t>3614-31-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>35136.09</v>
+        <v>54610.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2446-252-CM26</t>
+          <t>1395-120-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>40758.02</v>
+        <v>35136.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>527481-29-CM26</t>
+          <t>2446-252-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,22 +2424,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>62331.02</v>
+        <v>40758.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2448-230-CM26</t>
+          <t>527481-29-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,28 +2525,28 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>30107.74</v>
+        <v>62331.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3753-144-CM26</t>
+          <t>2448-230-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>79604.38</v>
+        <v>30107.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>703036-12-CM26</t>
+          <t>3753-144-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>69795.59</v>
+        <v>79604.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3712-361-CM26</t>
+          <t>703036-12-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>44295.21</v>
+        <v>69795.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2997-66-CM26</t>
+          <t>3712-361-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29091</v>
+        <v>44295.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1180825-16-CM26</t>
+          <t>2997-66-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,22 +2790,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>47413.1</v>
+        <v>29091</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>624-133-CM26</t>
+          <t>1180825-16-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,27 +2846,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>43688.38</v>
+        <v>47413.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>646-74-CM26</t>
+          <t>624-133-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,22 +2912,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30816.24</v>
+        <v>43688.38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3713-95-CM26</t>
+          <t>646-74-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>36317.99</v>
+        <v>30816.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3713-96-CM26</t>
+          <t>3713-95-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>762.03</v>
+        <v>36317.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>527481-81-CM26</t>
+          <t>3713-96-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>30303.8</v>
+        <v>762.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3754-198-CM26</t>
+          <t>527481-81-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,7 +3196,377 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
+        <v>30303.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3754-198-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>36103.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2446-901-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>38247.27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3707-454-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.040.200-9</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>35124.24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5158-100-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>147977.08</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4036-374-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.040.400-1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>50760.61</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3712-634-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>36228.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2431,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2561,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2626,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2691,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2756,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2943,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3008,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3073,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3321,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3386,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3451,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3450,7 +3594,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4036-374-CM26</t>
+          <t>5158-111-SE26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3465,22 +3609,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,82 +3634,216 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>50760.61</v>
+        <v>87066.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>5158-112-SE26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>29663.79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4036-374-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.040.400-1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>50760.61</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>3712-634-CM26</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>69.041.500-3</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>KOVACS SPA</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="n">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>36228.27</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -2821,7 +2821,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3516,7 +3520,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -3492,7 +3492,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -2858,7 +2858,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1099,7 +1099,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1094-3-CM25</t>
+          <t>539119-3510-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26458.93</v>
+        <v>31850.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>539119-3510-CM25</t>
+          <t>1094-3-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31850.29</v>
+        <v>26458.93</v>
       </c>
     </row>
     <row r="13">
@@ -2192,7 +2192,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>624-379-CM25</t>
+          <t>3754-1-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>382886.76</v>
+        <v>45526.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3754-1-CM26</t>
+          <t>624-379-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>45526.23</v>
+        <v>382886.76</v>
       </c>
     </row>
     <row r="30">
@@ -3853,6 +3853,67 @@
       </c>
       <c r="M53" s="2" t="n">
         <v>36228.27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>727202-233-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.040.500-8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>35756.62</v>
       </c>
     </row>
   </sheetData>
